--- a/E/EG2A.xlsx
+++ b/E/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="79">
   <si>
     <t/>
   </si>
@@ -94,103 +94,154 @@
     <t>RT</t>
   </si>
   <si>
-    <t>20094735</t>
-  </si>
-  <si>
-    <t>DOWNY SUNRISE 950 ML</t>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTQ 550 ML</t>
   </si>
   <si>
     <t>PT,(E-0.5B)</t>
   </si>
   <si>
-    <t>20094733</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTQ 875 ML</t>
-  </si>
-  <si>
-    <t>20132698</t>
-  </si>
-  <si>
-    <t>CLEAR SHP AK&amp;RNTK160</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20091441</t>
-  </si>
-  <si>
-    <t>CLEAR SHP KOMPLIT160</t>
+    <t>20074226</t>
+  </si>
+  <si>
+    <t>DOWNY S.FRSH 550 ML</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 550 ML</t>
+  </si>
+  <si>
+    <t>20141324</t>
+  </si>
+  <si>
+    <t>DOWNY S.SHINE 500 ML</t>
+  </si>
+  <si>
+    <t>20141642</t>
+  </si>
+  <si>
+    <t>NEXTPRIMEMEN BRIGHT</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20141643</t>
+  </si>
+  <si>
+    <t>NEXTPRIMEMEN DEEP</t>
+  </si>
+  <si>
+    <t>20079010</t>
+  </si>
+  <si>
+    <t>SHINZU'I FCL W 80 ML</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20091440</t>
-  </si>
-  <si>
-    <t>CLEAR SHP MENTHOL160</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20056356</t>
+  </si>
+  <si>
+    <t>SHINZU'I FW AC 80 ML</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>RT,(E-9B)</t>
+  </si>
+  <si>
+    <t>20129129</t>
+  </si>
+  <si>
+    <t>AZARINE CALM S 40 ML</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
     <t>20129130</t>
   </si>
   <si>
     <t>AZARINE HYD SS 30 ML</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20037566</t>
-  </si>
-  <si>
-    <t>SOVIA MNYK GR PCH 2L</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10008819</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 685G</t>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20117107</t>
+  </si>
+  <si>
+    <t>BANGO KCAP MNS 950 G</t>
   </si>
   <si>
     <t>RT,(E-0.5B)</t>
   </si>
   <si>
-    <t>20139930</t>
-  </si>
-  <si>
-    <t>WONHAE TPKI CHS TR80</t>
+    <t>10036553</t>
+  </si>
+  <si>
+    <t>PRONAS CORNED BF.340</t>
+  </si>
+  <si>
+    <t>20080924</t>
+  </si>
+  <si>
+    <t>YB BABY CRACK BNN 25</t>
+  </si>
+  <si>
+    <t>20092863</t>
+  </si>
+  <si>
+    <t>YB BABY CRCK STRW 25</t>
+  </si>
+  <si>
+    <t>20131331</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F CLWV TD10</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20142265</t>
-  </si>
-  <si>
-    <t>WONHAE TPKI CHS BU80</t>
-  </si>
-  <si>
-    <t>20087713</t>
-  </si>
-  <si>
-    <t>IDM NDL AYM PDS 90G</t>
-  </si>
-  <si>
-    <t>20142951</t>
-  </si>
-  <si>
-    <t>BEBELAC 1+ MADU 775</t>
+    <t>20131332</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F SKR LMI10</t>
+  </si>
+  <si>
+    <t>10006259</t>
+  </si>
+  <si>
+    <t>DANCOW FRTG 780 G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20065379</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+VNL  700 G</t>
+  </si>
+  <si>
+    <t>10033417</t>
+  </si>
+  <si>
+    <t>NTRILON R 4 VN 400 G</t>
   </si>
   <si>
     <t>20141306</t>
@@ -589,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -816,7 +867,7 @@
         <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -833,19 +884,19 @@
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
@@ -853,38 +904,38 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -893,90 +944,90 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -993,49 +1044,189 @@
         <v>21</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F24" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="E25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/E/EG2A.xlsx
+++ b/E/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="65">
   <si>
     <t/>
   </si>
   <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
+    <t>20143927</t>
+  </si>
+  <si>
+    <t>IDM HPY PNTS 3IN1 M8</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -31,223 +31,181 @@
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20114021</t>
-  </si>
-  <si>
-    <t>IDM TISU WJH PRM 100</t>
+    <t>20143926</t>
+  </si>
+  <si>
+    <t>IDM HPY PNTS 3IN1 L7</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20143785</t>
+  </si>
+  <si>
+    <t>IDM D/C AUTUM SNT700</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20143373</t>
+  </si>
+  <si>
+    <t>IDM KSET HNDK PRMIUM</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20087464</t>
+  </si>
+  <si>
+    <t>IDM PWNG PINK.PAS720</t>
+  </si>
+  <si>
+    <t>20137581</t>
+  </si>
+  <si>
+    <t>IDM PWNG EXO.BLUE720</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20001407</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI LAV 800</t>
+  </si>
+  <si>
+    <t>20001402</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI APL 800</t>
+  </si>
+  <si>
+    <t>20027997</t>
+  </si>
+  <si>
+    <t>IDM KAMPER NAPTLN150</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 920</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142275</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 920</t>
+  </si>
+  <si>
+    <t>20103266</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C H&amp;F 180</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20113915</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C SOFT 180</t>
+  </si>
+  <si>
+    <t>10006195</t>
+  </si>
+  <si>
+    <t>SARI ROTI CKL-KEJU</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20141506</t>
+  </si>
+  <si>
+    <t>RITZ CRACKER ORI 100</t>
+  </si>
+  <si>
+    <t>20134633</t>
+  </si>
+  <si>
+    <t>IDM MEISIS MIX 200G</t>
+  </si>
+  <si>
+    <t>10007973</t>
+  </si>
+  <si>
+    <t>BUAVITA MGGA 245 ML</t>
+  </si>
+  <si>
+    <t>20089806</t>
+  </si>
+  <si>
+    <t>OLATTE PEAR KLG 240</t>
+  </si>
+  <si>
+    <t>RT,(E-2.5B)</t>
+  </si>
+  <si>
+    <t>20036344</t>
+  </si>
+  <si>
+    <t>2BLIBIS SAUS CABE135</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10010805</t>
+  </si>
+  <si>
+    <t>SANIA MYK GR PCH 2 L</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10023780</t>
+  </si>
+  <si>
+    <t>DNCOW5+ MDU BX 750 G</t>
+  </si>
+  <si>
+    <t>20141306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDM COSMETIC </t>
+  </si>
+  <si>
     <t>PT</t>
-  </si>
-  <si>
-    <t>20045887</t>
-  </si>
-  <si>
-    <t>IDM TISU DP/HND 150S</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20103297</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP200</t>
-  </si>
-  <si>
-    <t>20115171</t>
-  </si>
-  <si>
-    <t>IDM TISU BAMBU 150'S</t>
-  </si>
-  <si>
-    <t>20035998</t>
-  </si>
-  <si>
-    <t>INDOMRET TRVL PACK50</t>
-  </si>
-  <si>
-    <t>20142611</t>
-  </si>
-  <si>
-    <t>IDM ALCHOL WIPE2X10S</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20141206</t>
-  </si>
-  <si>
-    <t>LARISST MN PCK 8X8'S</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTQ 550 ML</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20074226</t>
-  </si>
-  <si>
-    <t>DOWNY S.FRSH 550 ML</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 550 ML</t>
-  </si>
-  <si>
-    <t>20141324</t>
-  </si>
-  <si>
-    <t>DOWNY S.SHINE 500 ML</t>
-  </si>
-  <si>
-    <t>20141642</t>
-  </si>
-  <si>
-    <t>NEXTPRIMEMEN BRIGHT</t>
-  </si>
-  <si>
-    <t>RT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20141643</t>
-  </si>
-  <si>
-    <t>NEXTPRIMEMEN DEEP</t>
-  </si>
-  <si>
-    <t>20079010</t>
-  </si>
-  <si>
-    <t>SHINZU'I FCL W 80 ML</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20056356</t>
-  </si>
-  <si>
-    <t>SHINZU'I FW AC 80 ML</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>RT,(E-9B)</t>
-  </si>
-  <si>
-    <t>20129129</t>
-  </si>
-  <si>
-    <t>AZARINE CALM S 40 ML</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20129130</t>
-  </si>
-  <si>
-    <t>AZARINE HYD SS 30 ML</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20117107</t>
-  </si>
-  <si>
-    <t>BANGO KCAP MNS 950 G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>10036553</t>
-  </si>
-  <si>
-    <t>PRONAS CORNED BF.340</t>
-  </si>
-  <si>
-    <t>20080924</t>
-  </si>
-  <si>
-    <t>YB BABY CRACK BNN 25</t>
-  </si>
-  <si>
-    <t>20092863</t>
-  </si>
-  <si>
-    <t>YB BABY CRCK STRW 25</t>
-  </si>
-  <si>
-    <t>20131331</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F CLWV TD10</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20131332</t>
-  </si>
-  <si>
-    <t>AIRPRO A/F SKR LMI10</t>
-  </si>
-  <si>
-    <t>10006259</t>
-  </si>
-  <si>
-    <t>DANCOW FRTG 780 G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20065379</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+VNL  700 G</t>
-  </si>
-  <si>
-    <t>10033417</t>
-  </si>
-  <si>
-    <t>NTRILON R 4 VN 400 G</t>
-  </si>
-  <si>
-    <t>20141306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDM COSMETIC </t>
   </si>
 </sst>
 </file>
@@ -640,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -707,15 +665,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -724,58 +682,58 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -784,18 +742,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -804,18 +762,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -824,10 +782,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,33 +799,33 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,90 +839,90 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>44</v>
@@ -981,253 +939,153 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG2A.xlsx
+++ b/E/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="60">
   <si>
     <t/>
   </si>
@@ -109,103 +109,88 @@
     <t>7</t>
   </si>
   <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 920</t>
+    <t>20138903</t>
+  </si>
+  <si>
+    <t>SNSLK S G.BLC 320 ML</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138902</t>
+  </si>
+  <si>
+    <t>SNSLK S S.STH 320 ML</t>
+  </si>
+  <si>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SNLGHT JRK NPS 400 G</t>
+  </si>
+  <si>
+    <t>10005838</t>
+  </si>
+  <si>
+    <t>FILMA MYK GR RF 2 L</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20112371</t>
+  </si>
+  <si>
+    <t>GADJAH KP.TUBRUK 138</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20142275</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 920</t>
-  </si>
-  <si>
-    <t>20103266</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C H&amp;F 180</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20113915</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C SOFT 180</t>
-  </si>
-  <si>
-    <t>10006195</t>
-  </si>
-  <si>
-    <t>SARI ROTI CKL-KEJU</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20141506</t>
-  </si>
-  <si>
-    <t>RITZ CRACKER ORI 100</t>
-  </si>
-  <si>
     <t>20134633</t>
   </si>
   <si>
     <t>IDM MEISIS MIX 200G</t>
   </si>
   <si>
-    <t>10007973</t>
-  </si>
-  <si>
-    <t>BUAVITA MGGA 245 ML</t>
-  </si>
-  <si>
-    <t>20089806</t>
-  </si>
-  <si>
-    <t>OLATTE PEAR KLG 240</t>
-  </si>
-  <si>
-    <t>RT,(E-2.5B)</t>
-  </si>
-  <si>
-    <t>20036344</t>
-  </si>
-  <si>
-    <t>2BLIBIS SAUS CABE135</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10010805</t>
-  </si>
-  <si>
-    <t>SANIA MYK GR PCH 2 L</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10023780</t>
-  </si>
-  <si>
-    <t>DNCOW5+ MDU BX 750 G</t>
+    <t>20029222</t>
+  </si>
+  <si>
+    <t>PRONAS CORNED BEEF50</t>
+  </si>
+  <si>
+    <t>20051344</t>
+  </si>
+  <si>
+    <t>FITBAR CHOCOLATE 20G</t>
+  </si>
+  <si>
+    <t>20087019</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ MDU 1000 G</t>
+  </si>
+  <si>
+    <t>20066494</t>
+  </si>
+  <si>
+    <t>SGM EKSPL5+ MD 900 G</t>
   </si>
   <si>
     <t>20141306</t>
   </si>
   <si>
     <t xml:space="preserve">IDM COSMETIC </t>
-  </si>
-  <si>
-    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -598,14 +583,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -842,7 +827,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>34</v>
@@ -862,7 +847,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>34</v>
@@ -882,7 +867,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>39</v>
@@ -902,7 +887,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>39</v>
@@ -945,15 +930,15 @@
         <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -970,10 +955,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -985,15 +970,15 @@
         <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1005,7 +990,7 @@
         <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1019,10 +1004,10 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>24</v>
@@ -1030,30 +1015,30 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1062,30 +1047,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
